--- a/output/roomself_excel/6090.xlsx
+++ b/output/roomself_excel/6090.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>419147</v>
+        <v>67755</v>
       </c>
       <c r="D2" t="n">
-        <v>7404</v>
+        <v>2224</v>
       </c>
       <c r="E2" t="n">
-        <v>807</v>
+        <v>270</v>
       </c>
       <c r="F2" t="n">
-        <v>563</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>180540</v>
+        <v>282245</v>
       </c>
       <c r="D3" t="n">
-        <v>3484</v>
+        <v>4956</v>
       </c>
       <c r="E3" t="n">
-        <v>552</v>
+        <v>807</v>
       </c>
       <c r="F3" t="n">
-        <v>361</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50096</v>
+        <v>180540</v>
       </c>
       <c r="D4" t="n">
-        <v>1800</v>
+        <v>3484</v>
       </c>
       <c r="E4" t="n">
-        <v>248</v>
+        <v>552</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5">
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34056</v>
+        <v>50096</v>
       </c>
       <c r="D5" t="n">
-        <v>1480</v>
+        <v>1800</v>
       </c>
       <c r="E5" t="n">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="F5" t="n">
         <v>21</v>
@@ -554,19 +554,63 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>69147</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2192</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>34056</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1480</v>
+      </c>
+      <c r="E7" t="n">
+        <v>198</v>
+      </c>
+      <c r="F7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>34744</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D8" t="n">
         <v>1496</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E8" t="n">
         <v>223</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F8" t="n">
         <v>193</v>
       </c>
     </row>

--- a/output/roomself_excel/6090.xlsx
+++ b/output/roomself_excel/6090.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2224</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>270</v>
       </c>
-      <c r="F2" t="n">
-        <v>21</v>
-      </c>
+      <c r="G2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>4956</v>
       </c>
-      <c r="E3" t="n">
-        <v>807</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>452</v>
+        <v>765</v>
+      </c>
+      <c r="G3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>693</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>3484</v>
       </c>
-      <c r="E4" t="n">
-        <v>552</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>361</v>
+        <v>531</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>340</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +601,20 @@
       <c r="D5" t="n">
         <v>1800</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>248</v>
       </c>
-      <c r="F5" t="n">
-        <v>21</v>
-      </c>
+      <c r="G5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +631,12 @@
       <c r="D6" t="n">
         <v>2192</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +653,20 @@
       <c r="D7" t="n">
         <v>1480</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>198</v>
       </c>
-      <c r="F7" t="n">
-        <v>21</v>
-      </c>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +683,27 @@
       <c r="D8" t="n">
         <v>1496</v>
       </c>
-      <c r="E8" t="n">
-        <v>223</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>193</v>
+        <v>172</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>202</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
